--- a/data/trending_integrated_20261021_11.xlsx
+++ b/data/trending_integrated_20261021_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2425</v>
+        <v>2500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+26.04%</t>
+          <t>'+29.94%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H2" t="n">
         <v>3.94</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>9515968452</v>
+        <v>10119357902</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -670,13 +670,13 @@
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>81562777090</v>
+        <v>83143073910</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11260</v>
+        <v>11140</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.25%</t>
+          <t>'+14.02%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F4" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G4" t="n">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="H4" t="n">
         <v>1.28</v>
@@ -794,7 +794,7 @@
         <v>0.88</v>
       </c>
       <c r="O4" t="n">
-        <v>188398099985</v>
+        <v>199942410150</v>
       </c>
       <c r="P4" t="n">
         <v>11690</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇주 섹터 상승 및 신고가 경신 기대감. 미선물 폭등 및 연말 상승 전망.</t>
+          <t>로봇주 섹터 급등 속 신고가 재경신 기대감. 높은 변동성 속 매매 기회 포착.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇주', '신고가', '미선물']</t>
+          <t>['로봇주', '신고가', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9390</v>
+        <v>1319000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.55%</t>
+          <t>'+7.85%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.66</v>
+        <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>507</v>
       </c>
       <c r="G5" t="n">
-        <v>195</v>
+        <v>1455</v>
       </c>
       <c r="H5" t="n">
-        <v>5.34</v>
+        <v>48.77</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,91 +871,91 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8650</v>
+        <v>1223000</v>
       </c>
       <c r="K5" t="n">
-        <v>9010</v>
+        <v>1260000</v>
       </c>
       <c r="L5" t="n">
-        <v>9440</v>
+        <v>1329000</v>
       </c>
       <c r="M5" t="n">
-        <v>8790</v>
+        <v>1258000</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>48.81</v>
       </c>
       <c r="O5" t="n">
-        <v>16565458270</v>
+        <v>2684424235500</v>
       </c>
       <c r="P5" t="n">
-        <v>14940</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>5390</v>
+        <v>468000</v>
       </c>
       <c r="R5" t="n">
-        <v>225000</v>
+        <v>150000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>73000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>자회사 나스닥 상장 철회로 인한 중복 상장 금지 첫 적용. 테슬라 관련주.</t>
+          <t>자사주 매수와 외국인/기관 동반 매수로 인한 상승세. 반도체 수출 회복 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['테슬라', '중복상장', '나스닥']</t>
+          <t>['자사주 매수', '외국인 기관', '반도체 수출']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1320000</v>
+        <v>227250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.93%</t>
+          <t>'+7.45%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E6" t="n">
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="G6" t="n">
-        <v>1398</v>
+        <v>1720</v>
       </c>
       <c r="H6" t="n">
-        <v>48.77</v>
+        <v>46.08</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1223000</v>
+        <v>211500</v>
       </c>
       <c r="K6" t="n">
-        <v>1260000</v>
+        <v>217000</v>
       </c>
       <c r="L6" t="n">
-        <v>1328000</v>
+        <v>228000</v>
       </c>
       <c r="M6" t="n">
-        <v>1258000</v>
+        <v>217000</v>
       </c>
       <c r="N6" t="n">
-        <v>48.81</v>
+        <v>46.04</v>
       </c>
       <c r="O6" t="n">
-        <v>2545486064500</v>
+        <v>1766400055750</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>468000</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>150000</v>
+        <v>1981000</v>
       </c>
       <c r="S6" t="n">
-        <v>73000</v>
+        <v>380000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>반도체 수출 강세 및 차트상 V자 반등 가능성 언급. 기관/외인 매수세 유입 기대.</t>
+          <t>외국인 순매수세 유입과 4일 연속 매수로 인한 2차 랠리 시동 전망. 반도체 업황 개선 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체', '외국인', '차트']</t>
+          <t>['외국인 순매수', '반도체 업황', '2차 랠리']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>227000</v>
+        <v>9220</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.33%</t>
+          <t>'+6.59%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04</v>
+        <v>-0.66</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>85</v>
       </c>
       <c r="F7" t="n">
-        <v>497</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>1652</v>
+        <v>213</v>
       </c>
       <c r="H7" t="n">
-        <v>46.08</v>
+        <v>5.34</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>211500</v>
+        <v>8650</v>
       </c>
       <c r="K7" t="n">
-        <v>217000</v>
+        <v>9010</v>
       </c>
       <c r="L7" t="n">
-        <v>228000</v>
+        <v>9470</v>
       </c>
       <c r="M7" t="n">
-        <v>217000</v>
+        <v>8790</v>
       </c>
       <c r="N7" t="n">
-        <v>46.04</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>1672081189750</v>
+        <v>18698060635</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>14940</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>5390</v>
       </c>
       <c r="R7" t="n">
-        <v>1981000</v>
+        <v>225000</v>
       </c>
       <c r="S7" t="n">
-        <v>380000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외국인 순매수세 유입 및 반도체 시장 관련 긍정적 뉴스에 따른 상승 전망. 공매도 폐지 논의.</t>
+          <t>자회사 나스닥 상장 철회 결정으로 인한 호재 기대. 테슬라 관련 사업 성장 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외국인', '반도체', '공매도']</t>
+          <t>['상장 철회', '테슬라', '영업이익']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14730</v>
+        <v>14710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.03%</t>
+          <t>'+3.88%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H8" t="n">
         <v>9.82</v>
@@ -1162,7 +1162,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>15722711205</v>
+        <v>16132318865</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H9" t="n">
         <v>5.82</v>
@@ -1254,7 +1254,7 @@
         <v>5.91</v>
       </c>
       <c r="O9" t="n">
-        <v>15475984380</v>
+        <v>15595758070</v>
       </c>
       <c r="P9" t="n">
         <v>19950</v>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64500</v>
+        <v>64350</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.71%</t>
+          <t>'+2.47%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G10" t="n">
         <v>359</v>
@@ -1346,7 +1346,7 @@
         <v>22.29</v>
       </c>
       <c r="O10" t="n">
-        <v>48982611900</v>
+        <v>51200083550</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+2.35%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.93</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="H11" t="n">
         <v>0.84</v>
@@ -1438,7 +1438,7 @@
         <v>1.77</v>
       </c>
       <c r="O11" t="n">
-        <v>26427157838</v>
+        <v>26744534107</v>
       </c>
       <c r="P11" t="n">
         <v>2970</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7430</v>
+        <v>7440</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.20%</t>
+          <t>'+2.34%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G12" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="H12" t="n">
         <v>25.45</v>
@@ -1521,7 +1521,7 @@
         <v>7360</v>
       </c>
       <c r="L12" t="n">
-        <v>7430</v>
+        <v>7450</v>
       </c>
       <c r="M12" t="n">
         <v>7250</v>
@@ -1530,7 +1530,7 @@
         <v>25.4</v>
       </c>
       <c r="O12" t="n">
-        <v>6650922960</v>
+        <v>6995764900</v>
       </c>
       <c r="P12" t="n">
         <v>17950</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17680</v>
+        <v>17700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.08%</t>
+          <t>'+2.19%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="H13" t="n">
         <v>27.78</v>
@@ -1622,7 +1622,7 @@
         <v>27.78</v>
       </c>
       <c r="O13" t="n">
-        <v>22169276375</v>
+        <v>23140475105</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3045</v>
+        <v>3070</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.87%</t>
+          <t>'-5.10%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.73</v>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G14" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>0.73</v>
       </c>
       <c r="O14" t="n">
-        <v>7673381029</v>
+        <v>8320954961</v>
       </c>
       <c r="P14" t="n">
         <v>7050</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4315</v>
+        <v>4310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-6.80%</t>
+          <t>'-6.91%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="H15" t="n">
         <v>8.58</v>
@@ -1806,7 +1806,7 @@
         <v>8.57</v>
       </c>
       <c r="O15" t="n">
-        <v>16503101644</v>
+        <v>16838096656</v>
       </c>
       <c r="P15" t="n">
         <v>7560</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-19.08%</t>
+          <t>'-19.47%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H16" t="n">
         <v>0.6899999999999999</v>
@@ -1898,7 +1898,7 @@
         <v>0.57</v>
       </c>
       <c r="O16" t="n">
-        <v>16457215417</v>
+        <v>16624277062</v>
       </c>
       <c r="P16" t="n">
         <v>3980</v>

--- a/data/trending_integrated_20261021_11.xlsx
+++ b/data/trending_integrated_20261021_11.xlsx
@@ -578,13 +578,13 @@
         <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H2" t="n">
         <v>3.94</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10119357902</v>
+        <v>10168832902</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15000</v>
+        <v>14870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+24.17%</t>
+          <t>'+23.10%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>83143073910</v>
+        <v>83797356185</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11140</v>
+        <v>11000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.02%</t>
+          <t>'+12.59%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="H4" t="n">
         <v>1.28</v>
@@ -794,7 +794,7 @@
         <v>0.88</v>
       </c>
       <c r="O4" t="n">
-        <v>199942410150</v>
+        <v>212842727905</v>
       </c>
       <c r="P4" t="n">
         <v>11690</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇주 섹터 급등 속 신고가 재경신 기대감. 높은 변동성 속 매매 기회 포착.</t>
+          <t>HT로보틱스 신고가 경신 기대감. 로봇주 섹터 내 대장주로서의 강세 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇주', '신고가', '급등']</t>
+          <t>['신고가', '로봇주', '섹터']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1319000</v>
+        <v>9320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.85%</t>
+          <t>'+7.75%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.04</v>
+        <v>-0.66</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>84</v>
       </c>
       <c r="F5" t="n">
-        <v>507</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>1455</v>
+        <v>210</v>
       </c>
       <c r="H5" t="n">
-        <v>48.77</v>
+        <v>5.34</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1223000</v>
+        <v>8650</v>
       </c>
       <c r="K5" t="n">
-        <v>1260000</v>
+        <v>9010</v>
       </c>
       <c r="L5" t="n">
-        <v>1329000</v>
+        <v>9470</v>
       </c>
       <c r="M5" t="n">
-        <v>1258000</v>
+        <v>8790</v>
       </c>
       <c r="N5" t="n">
-        <v>48.81</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>2684424235500</v>
+        <v>19733084260</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>14940</v>
       </c>
       <c r="Q5" t="n">
-        <v>468000</v>
+        <v>5390</v>
       </c>
       <c r="R5" t="n">
-        <v>150000</v>
+        <v>225000</v>
       </c>
       <c r="S5" t="n">
-        <v>73000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>자사주 매수와 외국인/기관 동반 매수로 인한 상승세. 반도체 수출 회복 기대감.</t>
+          <t>명신산업 자회사 나스닥 상장 철회 결정. 테슬라 관련 사업 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['자사주 매수', '외국인 기관', '반도체 수출']</t>
+          <t>['나스닥 상장 철회', '테슬라', '영업이익']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>227250</v>
+        <v>1312000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.45%</t>
+          <t>'+7.28%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E6" t="n">
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="G6" t="n">
-        <v>1720</v>
+        <v>1534</v>
       </c>
       <c r="H6" t="n">
-        <v>46.08</v>
+        <v>48.77</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>211500</v>
+        <v>1223000</v>
       </c>
       <c r="K6" t="n">
-        <v>217000</v>
+        <v>1260000</v>
       </c>
       <c r="L6" t="n">
-        <v>228000</v>
+        <v>1329000</v>
       </c>
       <c r="M6" t="n">
-        <v>217000</v>
+        <v>1258000</v>
       </c>
       <c r="N6" t="n">
-        <v>46.04</v>
+        <v>48.81</v>
       </c>
       <c r="O6" t="n">
-        <v>1766400055750</v>
+        <v>2779661401000</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>468000</v>
       </c>
       <c r="R6" t="n">
-        <v>1981000</v>
+        <v>150000</v>
       </c>
       <c r="S6" t="n">
-        <v>380000</v>
+        <v>73000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외국인 순매수세 유입과 4일 연속 매수로 인한 2차 랠리 시동 전망. 반도체 업황 개선 기대.</t>
+          <t>자사주 매입 후 주가 반등 기대감. 솔리다임 상장 확정 소식.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외국인 순매수', '반도체 업황', '2차 랠리']</t>
+          <t>['자사주 매입', '솔리다임', '반등']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9220</v>
+        <v>226000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.59%</t>
+          <t>'+6.86%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.66</v>
+        <v>0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>499</v>
       </c>
       <c r="G7" t="n">
-        <v>213</v>
+        <v>1730</v>
       </c>
       <c r="H7" t="n">
-        <v>5.34</v>
+        <v>46.08</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8650</v>
+        <v>211500</v>
       </c>
       <c r="K7" t="n">
-        <v>9010</v>
+        <v>217000</v>
       </c>
       <c r="L7" t="n">
-        <v>9470</v>
+        <v>228000</v>
       </c>
       <c r="M7" t="n">
-        <v>8790</v>
+        <v>217000</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>46.04</v>
       </c>
       <c r="O7" t="n">
-        <v>18698060635</v>
+        <v>1838259210750</v>
       </c>
       <c r="P7" t="n">
-        <v>14940</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>5390</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>225000</v>
+        <v>1981000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>380000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>자회사 나스닥 상장 철회 결정으로 인한 호재 기대. 테슬라 관련 사업 성장 전망.</t>
+          <t>외인 순매수와 함께 2차 랠리 시동 전망. 공매도 세력에 대한 경고 메시지.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['상장 철회', '테슬라', '영업이익']</t>
+          <t>['외인 수급', '공매도', '2차 랠리']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14710</v>
+        <v>14700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.88%</t>
+          <t>'+3.81%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
         <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H8" t="n">
         <v>9.82</v>
@@ -1162,7 +1162,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>16132318865</v>
+        <v>17024076855</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1222,13 +1222,13 @@
         <v>-0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="H9" t="n">
         <v>5.82</v>
@@ -1254,7 +1254,7 @@
         <v>5.91</v>
       </c>
       <c r="O9" t="n">
-        <v>15595758070</v>
+        <v>15728082670</v>
       </c>
       <c r="P9" t="n">
         <v>19950</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64350</v>
+        <v>7440</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.47%</t>
+          <t>'+2.34%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="F10" t="n">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>359</v>
+        <v>209</v>
       </c>
       <c r="H10" t="n">
-        <v>22.23</v>
+        <v>25.45</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>62800</v>
+        <v>7270</v>
       </c>
       <c r="K10" t="n">
-        <v>63600</v>
+        <v>7360</v>
       </c>
       <c r="L10" t="n">
-        <v>64800</v>
+        <v>7450</v>
       </c>
       <c r="M10" t="n">
-        <v>62600</v>
+        <v>7250</v>
       </c>
       <c r="N10" t="n">
-        <v>22.29</v>
+        <v>25.4</v>
       </c>
       <c r="O10" t="n">
-        <v>51200083550</v>
+        <v>7336430265</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>7190</v>
       </c>
       <c r="R10" t="n">
-        <v>-40000</v>
+        <v>131000</v>
       </c>
       <c r="S10" t="n">
-        <v>-3000</v>
+        <v>-2000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SMR 및 원전 관련 사업 기대감에도 불구, 외인 매도 및 정부 정책 불만에 따른 주가 부진. 반등 노력.</t>
+          <t>개인 투자자들의 피로감과 회사의 저평가 및 상폐 가능성 언급. 외국인 비중 변화 및 주가 흐름에 대한 부정적 시각.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['SMR', '원전', '외인']</t>
+          <t>['개인 투자자', '상폐 가능성', '저평가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1610</v>
+        <v>64200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.35%</t>
+          <t>'+2.23%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.93</v>
+        <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="G11" t="n">
-        <v>174</v>
+        <v>381</v>
       </c>
       <c r="H11" t="n">
-        <v>0.84</v>
+        <v>22.23</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1573</v>
+        <v>62800</v>
       </c>
       <c r="K11" t="n">
-        <v>1650</v>
+        <v>63600</v>
       </c>
       <c r="L11" t="n">
-        <v>1715</v>
+        <v>64800</v>
       </c>
       <c r="M11" t="n">
-        <v>1573</v>
+        <v>62600</v>
       </c>
       <c r="N11" t="n">
-        <v>1.77</v>
+        <v>22.29</v>
       </c>
       <c r="O11" t="n">
-        <v>26744534107</v>
+        <v>52243310100</v>
       </c>
       <c r="P11" t="n">
-        <v>2970</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>890</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>-746000</v>
+        <v>-40000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>스페이스X 수혜 기대감 속 거래량 증가. 단기 급등 가능성 있으나 윗꼬리 부담.</t>
+          <t>SMR 사업 관련 기대감에도 불구하고 주가 부진 지속. 공매도 및 시장 상황에 대한 불만.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['스페이스X', '수혜주', '거래량']</t>
+          <t>['SMR', '공매도', '주가 부진']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7440</v>
+        <v>17680</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.34%</t>
+          <t>'+2.08%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="H12" t="n">
-        <v>25.45</v>
+        <v>27.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7270</v>
+        <v>17320</v>
       </c>
       <c r="K12" t="n">
-        <v>7360</v>
+        <v>17480</v>
       </c>
       <c r="L12" t="n">
-        <v>7450</v>
+        <v>17820</v>
       </c>
       <c r="M12" t="n">
-        <v>7250</v>
+        <v>17170</v>
       </c>
       <c r="N12" t="n">
-        <v>25.4</v>
+        <v>27.78</v>
       </c>
       <c r="O12" t="n">
-        <v>6995764900</v>
+        <v>24064549745</v>
       </c>
       <c r="P12" t="n">
-        <v>17950</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>7190</v>
+        <v>17170</v>
       </c>
       <c r="R12" t="n">
-        <v>131000</v>
+        <v>146000</v>
       </c>
       <c r="S12" t="n">
-        <v>-2000</v>
+        <v>24000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>개인 투자자들의 피로감과 회사의 저평가 및 상폐 가능성 언급. 외국인 비중 변화 및 주가 흐름에 대한 부정적 시각.</t>
+          <t>정치적 비난과 함께 실적 및 조선업 섹터 전반에 대한 부정적 전망. 반도체 섹터로의 이동 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['개인 투자자', '상폐 가능성', '저평가']</t>
+          <t>['조선업', '실적 부진', '반도체 이동']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17700</v>
+        <v>1604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.19%</t>
+          <t>'+1.97%</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="E13" t="n">
+        <v>64</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42</v>
+      </c>
+      <c r="G13" t="n">
+        <v>182</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1573</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1650</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1715</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1573</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O13" t="n">
+        <v>26989856819</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2970</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>890</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-746000</v>
+      </c>
+      <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>72</v>
-      </c>
-      <c r="F13" t="n">
-        <v>43</v>
-      </c>
-      <c r="G13" t="n">
-        <v>161</v>
-      </c>
-      <c r="H13" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>17320</v>
-      </c>
-      <c r="K13" t="n">
-        <v>17480</v>
-      </c>
-      <c r="L13" t="n">
-        <v>17820</v>
-      </c>
-      <c r="M13" t="n">
-        <v>17170</v>
-      </c>
-      <c r="N13" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="O13" t="n">
-        <v>23140475105</v>
-      </c>
-      <c r="P13" t="n">
-        <v>35350</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>17170</v>
-      </c>
-      <c r="R13" t="n">
-        <v>146000</v>
-      </c>
-      <c r="S13" t="n">
-        <v>24000</v>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 비난과 함께 실적 및 조선업 섹터 전반에 대한 부정적 전망. 반도체 섹터로의 이동 언급.</t>
+          <t>스페이스X 수혜 기대감 속 거래량 증가. 단기 급등 가능성 있으나 윗꼬리 부담.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조선업', '실적 부진', '반도체 이동']</t>
+          <t>['스페이스X', '수혜주', '거래량']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3070</v>
+        <v>3080</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.10%</t>
+          <t>'-4.79%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.73</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>0.73</v>
       </c>
       <c r="O14" t="n">
-        <v>8320954961</v>
+        <v>8547664401</v>
       </c>
       <c r="P14" t="n">
         <v>7050</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4310</v>
+        <v>4300</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-6.91%</t>
+          <t>'-7.13%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="H15" t="n">
         <v>8.58</v>
@@ -1806,7 +1806,7 @@
         <v>8.57</v>
       </c>
       <c r="O15" t="n">
-        <v>16838096656</v>
+        <v>17240783173</v>
       </c>
       <c r="P15" t="n">
         <v>7560</v>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1224</v>
+        <v>1255</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-19.47%</t>
+          <t>'-17.43%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.12</v>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
         <v>56</v>
@@ -1898,7 +1898,7 @@
         <v>0.57</v>
       </c>
       <c r="O16" t="n">
-        <v>16624277062</v>
+        <v>17112946867</v>
       </c>
       <c r="P16" t="n">
         <v>3980</v>

--- a/data/trending_integrated_20261021_11.xlsx
+++ b/data/trending_integrated_20261021_11.xlsx
@@ -578,13 +578,13 @@
         <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
         <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H2" t="n">
         <v>3.94</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10168832902</v>
+        <v>10228027902</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14870</v>
+        <v>14950</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.10%</t>
+          <t>'+23.76%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>83797356185</v>
+        <v>84995055715</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11000</v>
+        <v>11130</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.59%</t>
+          <t>'+13.92%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F4" t="n">
         <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="H4" t="n">
         <v>1.28</v>
@@ -794,7 +794,7 @@
         <v>0.88</v>
       </c>
       <c r="O4" t="n">
-        <v>212842727905</v>
+        <v>219629317140</v>
       </c>
       <c r="P4" t="n">
         <v>11690</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HT로보틱스 신고가 경신 기대감. 로봇주 섹터 내 대장주로서의 강세 전망.</t>
+          <t>HT로보틱스 신고가 경신. 로봇주 섹터 강세. 개미 털기 후 조용한 게시판, 신고가 기반 상승 지속 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['신고가', '로봇주', '섹터']</t>
+          <t>['신고가', '로봇주', '주가 상승']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9320</v>
+        <v>9350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.75%</t>
+          <t>'+8.09%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.66</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="H5" t="n">
         <v>5.34</v>
@@ -886,7 +886,7 @@
         <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>19733084260</v>
+        <v>20067079885</v>
       </c>
       <c r="P5" t="n">
         <v>14940</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>명신산업 자회사 나스닥 상장 철회 결정. 테슬라 관련 사업 기대감.</t>
+          <t>자회사 나스닥 상장 철회 공시. 중복상장 금지 첫 적용. 4천억대 시총 및 1200억 이상 영업이익 기반 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['나스닥 상장 철회', '테슬라', '영업이익']</t>
+          <t>['나스닥 상장 철회', '중복상장 금지', '영업이익']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1312000</v>
+        <v>1308000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.28%</t>
+          <t>'+6.95%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="G6" t="n">
-        <v>1534</v>
+        <v>1619</v>
       </c>
       <c r="H6" t="n">
         <v>48.77</v>
@@ -978,7 +978,7 @@
         <v>48.81</v>
       </c>
       <c r="O6" t="n">
-        <v>2779661401000</v>
+        <v>2845552325500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>자사주 매입 후 주가 반등 기대감. 솔리다임 상장 확정 소식.</t>
+          <t>자사주 매입 완료 후 외인, 기관 동반 매수세 유입. 120만원 지지선 확인. 반등 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['자사주 매입', '솔리다임', '반등']</t>
+          <t>['자사주 매입', '외인 기관 매수', '반등']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>226000</v>
+        <v>225750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.86%</t>
+          <t>'+6.74%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="G7" t="n">
-        <v>1730</v>
+        <v>1756</v>
       </c>
       <c r="H7" t="n">
         <v>46.08</v>
@@ -1070,7 +1070,7 @@
         <v>46.04</v>
       </c>
       <c r="O7" t="n">
-        <v>1838259210750</v>
+        <v>1888850389250</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외인 순매수와 함께 2차 랠리 시동 전망. 공매도 세력에 대한 경고 메시지.</t>
+          <t>미국 중국 반도체 퇴출 결정에 따른 외인 대규모 순매수 유입. 4만원 목표 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외인 수급', '공매도', '2차 랠리']</t>
+          <t>['반도체', '외인 순매수', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14700</v>
+        <v>14660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.81%</t>
+          <t>'+3.53%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
         <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="H8" t="n">
         <v>9.82</v>
@@ -1162,7 +1162,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>17024076855</v>
+        <v>17431704860</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>주가 하락 및 윗꼬리 음봉 형성. 공매도 집중 및 실적 기대감 부재.</t>
+          <t>외국인, 연기금 순매수세 확인. 목표가 5만원 제시. 대차해지 중요성 강조. 정치적 이슈 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '실적']</t>
+          <t>['외인 연기금', '실적주', '목표가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2920</v>
+        <v>2925</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.82%</t>
+          <t>'+2.99%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1254,7 +1254,7 @@
         <v>5.91</v>
       </c>
       <c r="O9" t="n">
-        <v>15728082670</v>
+        <v>15861029544</v>
       </c>
       <c r="P9" t="n">
         <v>19950</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7440</v>
+        <v>7470</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.34%</t>
+          <t>'+2.75%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H10" t="n">
         <v>25.45</v>
@@ -1337,7 +1337,7 @@
         <v>7360</v>
       </c>
       <c r="L10" t="n">
-        <v>7450</v>
+        <v>7480</v>
       </c>
       <c r="M10" t="n">
         <v>7250</v>
@@ -1346,7 +1346,7 @@
         <v>25.4</v>
       </c>
       <c r="O10" t="n">
-        <v>7336430265</v>
+        <v>7882703985</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>64200</v>
+        <v>17710</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.23%</t>
+          <t>'+2.25%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="F11" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>381</v>
+        <v>174</v>
       </c>
       <c r="H11" t="n">
-        <v>22.23</v>
+        <v>27.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>62800</v>
+        <v>17320</v>
       </c>
       <c r="K11" t="n">
-        <v>63600</v>
+        <v>17480</v>
       </c>
       <c r="L11" t="n">
-        <v>64800</v>
+        <v>17820</v>
       </c>
       <c r="M11" t="n">
-        <v>62600</v>
+        <v>17170</v>
       </c>
       <c r="N11" t="n">
-        <v>22.29</v>
+        <v>27.78</v>
       </c>
       <c r="O11" t="n">
-        <v>52243310100</v>
+        <v>25230377560</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>17170</v>
       </c>
       <c r="R11" t="n">
-        <v>-40000</v>
+        <v>146000</v>
       </c>
       <c r="S11" t="n">
-        <v>-3000</v>
+        <v>24000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>SMR 사업 관련 기대감에도 불구하고 주가 부진 지속. 공매도 및 시장 상황에 대한 불만.</t>
+          <t>정치적 비난과 함께 실적 및 조선업 섹터 전반에 대한 부정적 전망. 반도체 섹터로의 이동 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['SMR', '공매도', '주가 부진']</t>
+          <t>['조선업', '실적 부진', '반도체 이동']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17680</v>
+        <v>64100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.08%</t>
+          <t>'+2.07%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="G12" t="n">
-        <v>163</v>
+        <v>378</v>
       </c>
       <c r="H12" t="n">
-        <v>27.78</v>
+        <v>22.23</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,60 +1515,60 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17320</v>
+        <v>62800</v>
       </c>
       <c r="K12" t="n">
-        <v>17480</v>
+        <v>63600</v>
       </c>
       <c r="L12" t="n">
-        <v>17820</v>
+        <v>64800</v>
       </c>
       <c r="M12" t="n">
-        <v>17170</v>
+        <v>62600</v>
       </c>
       <c r="N12" t="n">
-        <v>27.78</v>
+        <v>22.29</v>
       </c>
       <c r="O12" t="n">
-        <v>24064549745</v>
+        <v>54293948300</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>17170</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>146000</v>
+        <v>-40000</v>
       </c>
       <c r="S12" t="n">
-        <v>24000</v>
+        <v>-3000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 비난과 함께 실적 및 조선업 섹터 전반에 대한 부정적 전망. 반도체 섹터로의 이동 언급.</t>
+          <t>야간선물 폭등에도 불구하고 국내 주식장 하락. 외인 매도 및 정부 정책 무능력 비판. 공매도 금지 청원 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선업', '실적 부진', '반도체 이동']</t>
+          <t>['공매도', '외인 매도', '정부 정책']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1590,13 +1590,13 @@
         <v>-0.93</v>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" t="n">
         <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H13" t="n">
         <v>0.84</v>
@@ -1622,7 +1622,7 @@
         <v>1.77</v>
       </c>
       <c r="O13" t="n">
-        <v>26989856819</v>
+        <v>27169486035</v>
       </c>
       <c r="P13" t="n">
         <v>2970</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3080</v>
+        <v>3060</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.79%</t>
+          <t>'-5.41%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.73</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
         <v>30</v>
       </c>
       <c r="G14" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>0.73</v>
       </c>
       <c r="O14" t="n">
-        <v>8547664401</v>
+        <v>8683188458</v>
       </c>
       <c r="P14" t="n">
         <v>7050</v>
@@ -1774,13 +1774,13 @@
         <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="H15" t="n">
         <v>8.58</v>
@@ -1806,7 +1806,7 @@
         <v>8.57</v>
       </c>
       <c r="O15" t="n">
-        <v>17240783173</v>
+        <v>17466593918</v>
       </c>
       <c r="P15" t="n">
         <v>7560</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1255</v>
+        <v>1264</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-17.43%</t>
+          <t>'-16.84%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.12</v>
       </c>
       <c r="E16" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F16" t="n">
         <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="H16" t="n">
         <v>0.6899999999999999</v>
@@ -1898,7 +1898,7 @@
         <v>0.57</v>
       </c>
       <c r="O16" t="n">
-        <v>17112946867</v>
+        <v>17585068639</v>
       </c>
       <c r="P16" t="n">
         <v>3980</v>

--- a/data/trending_integrated_20261021_11.xlsx
+++ b/data/trending_integrated_20261021_11.xlsx
@@ -578,13 +578,13 @@
         <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
         <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="H2" t="n">
         <v>3.94</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10228027902</v>
+        <v>10552125257</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14950</v>
+        <v>14920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.76%</t>
+          <t>'+23.51%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>84995055715</v>
+        <v>85393420450</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11130</v>
+        <v>11150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.92%</t>
+          <t>'+14.12%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F4" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="H4" t="n">
         <v>1.28</v>
@@ -794,7 +794,7 @@
         <v>0.88</v>
       </c>
       <c r="O4" t="n">
-        <v>219629317140</v>
+        <v>224385250390</v>
       </c>
       <c r="P4" t="n">
         <v>11690</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9350</v>
+        <v>9300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.09%</t>
+          <t>'+7.51%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.66</v>
       </c>
       <c r="E5" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
         <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H5" t="n">
         <v>5.34</v>
@@ -886,7 +886,7 @@
         <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>20067079885</v>
+        <v>20294422375</v>
       </c>
       <c r="P5" t="n">
         <v>14940</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1308000</v>
+        <v>225250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.95%</t>
+          <t>'+6.50%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E6" t="n">
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="G6" t="n">
-        <v>1619</v>
+        <v>1751</v>
       </c>
       <c r="H6" t="n">
-        <v>48.77</v>
+        <v>46.08</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1223000</v>
+        <v>211500</v>
       </c>
       <c r="K6" t="n">
-        <v>1260000</v>
+        <v>217000</v>
       </c>
       <c r="L6" t="n">
-        <v>1329000</v>
+        <v>228000</v>
       </c>
       <c r="M6" t="n">
-        <v>1258000</v>
+        <v>217000</v>
       </c>
       <c r="N6" t="n">
-        <v>48.81</v>
+        <v>46.04</v>
       </c>
       <c r="O6" t="n">
-        <v>2845552325500</v>
+        <v>1948397905500</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>468000</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>150000</v>
+        <v>1981000</v>
       </c>
       <c r="S6" t="n">
-        <v>73000</v>
+        <v>380000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>자사주 매입 완료 후 외인, 기관 동반 매수세 유입. 120만원 지지선 확인. 반등 기대.</t>
+          <t>외인 순매수 동반하며 반도체 퇴출 결정 관련 상승 기대. 2차 랠리 및 60만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['자사주 매입', '외인 기관 매수', '반등']</t>
+          <t>['외인 순매수', '반도체 퇴출', '2차 랠리']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>225750</v>
+        <v>1299000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.74%</t>
+          <t>'+6.21%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E7" t="n">
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="G7" t="n">
-        <v>1756</v>
+        <v>1662</v>
       </c>
       <c r="H7" t="n">
-        <v>46.08</v>
+        <v>48.77</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>211500</v>
+        <v>1223000</v>
       </c>
       <c r="K7" t="n">
-        <v>217000</v>
+        <v>1260000</v>
       </c>
       <c r="L7" t="n">
-        <v>228000</v>
+        <v>1329000</v>
       </c>
       <c r="M7" t="n">
-        <v>217000</v>
+        <v>1258000</v>
       </c>
       <c r="N7" t="n">
-        <v>46.04</v>
+        <v>48.81</v>
       </c>
       <c r="O7" t="n">
-        <v>1888850389250</v>
+        <v>2912670189500</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>468000</v>
       </c>
       <c r="R7" t="n">
-        <v>1981000</v>
+        <v>150000</v>
       </c>
       <c r="S7" t="n">
-        <v>380000</v>
+        <v>73000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 중국 반도체 퇴출 결정에 따른 외인 대규모 순매수 유입. 4만원 목표 전망.</t>
+          <t>자사주 매입 완료 후 숨통 트임. 외인, 기관 동반 매수세 유입으로 반등 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체', '외인 순매수', '목표가']</t>
+          <t>['자사주 매입', '외인 기관', '반등']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14660</v>
+        <v>14690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.53%</t>
+          <t>'+3.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1162,7 +1162,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>17431704860</v>
+        <v>19681884090</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1207,70 +1207,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2925</v>
+        <v>7470</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.99%</t>
+          <t>'+2.75%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.09</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
         <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="H9" t="n">
-        <v>5.82</v>
+        <v>25.45</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2840</v>
+        <v>7270</v>
       </c>
       <c r="K9" t="n">
-        <v>3100</v>
+        <v>7360</v>
       </c>
       <c r="L9" t="n">
-        <v>3300</v>
+        <v>7490</v>
       </c>
       <c r="M9" t="n">
-        <v>2855</v>
+        <v>7250</v>
       </c>
       <c r="N9" t="n">
-        <v>5.91</v>
+        <v>25.4</v>
       </c>
       <c r="O9" t="n">
-        <v>15861029544</v>
+        <v>8255866350</v>
       </c>
       <c r="P9" t="n">
-        <v>19950</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>1913</v>
+        <v>7190</v>
       </c>
       <c r="R9" t="n">
-        <v>-1166000</v>
+        <v>131000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
+          <t>개인 투자자들의 피로감과 회사의 저평가 및 상폐 가능성 언급. 외국인 비중 변화 및 주가 흐름에 대한 부정적 시각.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['우주섹터', '주가조작', '투자기업']</t>
+          <t>['개인 투자자', '상폐 가능성', '저평가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,77 +1292,77 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7470</v>
+        <v>2915</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.75%</t>
+          <t>'+2.64%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
         <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="H10" t="n">
-        <v>25.45</v>
+        <v>5.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7270</v>
+        <v>2840</v>
       </c>
       <c r="K10" t="n">
-        <v>7360</v>
+        <v>3100</v>
       </c>
       <c r="L10" t="n">
-        <v>7480</v>
+        <v>3300</v>
       </c>
       <c r="M10" t="n">
-        <v>7250</v>
+        <v>2855</v>
       </c>
       <c r="N10" t="n">
-        <v>25.4</v>
+        <v>5.91</v>
       </c>
       <c r="O10" t="n">
-        <v>7882703985</v>
+        <v>15891727104</v>
       </c>
       <c r="P10" t="n">
-        <v>17950</v>
+        <v>19950</v>
       </c>
       <c r="Q10" t="n">
-        <v>7190</v>
+        <v>1913</v>
       </c>
       <c r="R10" t="n">
-        <v>131000</v>
+        <v>-1166000</v>
       </c>
       <c r="S10" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>개인 투자자들의 피로감과 회사의 저평가 및 상폐 가능성 언급. 외국인 비중 변화 및 주가 흐름에 대한 부정적 시각.</t>
+          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['개인 투자자', '상폐 가능성', '저평가']</t>
+          <t>['우주섹터', '주가조작', '투자기업']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17710</v>
+        <v>64200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.25%</t>
+          <t>'+2.23%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="G11" t="n">
-        <v>174</v>
+        <v>388</v>
       </c>
       <c r="H11" t="n">
-        <v>27.78</v>
+        <v>22.23</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17320</v>
+        <v>62800</v>
       </c>
       <c r="K11" t="n">
-        <v>17480</v>
+        <v>63600</v>
       </c>
       <c r="L11" t="n">
-        <v>17820</v>
+        <v>64800</v>
       </c>
       <c r="M11" t="n">
-        <v>17170</v>
+        <v>62600</v>
       </c>
       <c r="N11" t="n">
-        <v>27.78</v>
+        <v>22.29</v>
       </c>
       <c r="O11" t="n">
-        <v>25230377560</v>
+        <v>55807417850</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>17170</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>146000</v>
+        <v>-40000</v>
       </c>
       <c r="S11" t="n">
-        <v>24000</v>
+        <v>-3000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 비난과 함께 실적 및 조선업 섹터 전반에 대한 부정적 전망. 반도체 섹터로의 이동 언급.</t>
+          <t>야간 선물 상승에도 불구하고 국내 증시 하락세 지속. 공매도 금지 청원 등 규제 완화 요구.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선업', '실적 부진', '반도체 이동']</t>
+          <t>['공매도', '주가 누르기', '규제 완화']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>64100</v>
+        <v>17700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.07%</t>
+          <t>'+2.19%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="F12" t="n">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>378</v>
+        <v>172</v>
       </c>
       <c r="H12" t="n">
-        <v>22.23</v>
+        <v>27.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,60 +1515,60 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>62800</v>
+        <v>17320</v>
       </c>
       <c r="K12" t="n">
-        <v>63600</v>
+        <v>17480</v>
       </c>
       <c r="L12" t="n">
-        <v>64800</v>
+        <v>17820</v>
       </c>
       <c r="M12" t="n">
-        <v>62600</v>
+        <v>17170</v>
       </c>
       <c r="N12" t="n">
-        <v>22.29</v>
+        <v>27.78</v>
       </c>
       <c r="O12" t="n">
-        <v>54293948300</v>
+        <v>25710026415</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>17170</v>
       </c>
       <c r="R12" t="n">
-        <v>-40000</v>
+        <v>146000</v>
       </c>
       <c r="S12" t="n">
-        <v>-3000</v>
+        <v>24000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>야간선물 폭등에도 불구하고 국내 주식장 하락. 외인 매도 및 정부 정책 무능력 비판. 공매도 금지 청원 제기.</t>
+          <t>정치적 비난과 함께 실적 및 조선업 섹터 전반에 대한 부정적 전망. 반도체 섹터로의 이동 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '외인 매도', '정부 정책']</t>
+          <t>['조선업', '실적 부진', '반도체 이동']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1604</v>
+        <v>1599</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.97%</t>
+          <t>'+1.65%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.93</v>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="H13" t="n">
         <v>0.84</v>
@@ -1622,7 +1622,7 @@
         <v>1.77</v>
       </c>
       <c r="O13" t="n">
-        <v>27169486035</v>
+        <v>27333259726</v>
       </c>
       <c r="P13" t="n">
         <v>2970</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3060</v>
+        <v>3100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.41%</t>
+          <t>'-4.17%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1714,7 +1714,7 @@
         <v>0.73</v>
       </c>
       <c r="O14" t="n">
-        <v>8683188458</v>
+        <v>9086558468</v>
       </c>
       <c r="P14" t="n">
         <v>7050</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4300</v>
+        <v>4287</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.13%</t>
+          <t>'-7.41%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>361</v>
+        <v>396</v>
       </c>
       <c r="H15" t="n">
         <v>8.58</v>
@@ -1806,7 +1806,7 @@
         <v>8.57</v>
       </c>
       <c r="O15" t="n">
-        <v>17466593918</v>
+        <v>17913706501</v>
       </c>
       <c r="P15" t="n">
         <v>7560</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1264</v>
+        <v>1248</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-16.84%</t>
+          <t>'-17.89%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.12</v>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G16" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H16" t="n">
         <v>0.6899999999999999</v>
@@ -1898,7 +1898,7 @@
         <v>0.57</v>
       </c>
       <c r="O16" t="n">
-        <v>17585068639</v>
+        <v>17749324079</v>
       </c>
       <c r="P16" t="n">
         <v>3980</v>

--- a/data/trending_integrated_20261021_11.xlsx
+++ b/data/trending_integrated_20261021_11.xlsx
@@ -578,13 +578,13 @@
         <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F2" t="n">
         <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H2" t="n">
         <v>3.94</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10552125257</v>
+        <v>10561557757</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14920</v>
+        <v>15080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.51%</t>
+          <t>'+24.83%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>85393420450</v>
+        <v>87046396610</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11150</v>
+        <v>11240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.12%</t>
+          <t>'+15.05%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G4" t="n">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="H4" t="n">
         <v>1.28</v>
@@ -794,7 +794,7 @@
         <v>0.88</v>
       </c>
       <c r="O4" t="n">
-        <v>224385250390</v>
+        <v>229804008710</v>
       </c>
       <c r="P4" t="n">
         <v>11690</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HT로보틱스 신고가 경신. 로봇주 섹터 강세. 개미 털기 후 조용한 게시판, 신고가 기반 상승 지속 전망.</t>
+          <t>역사적 신고가 경신하며 강한 상승세. 인공지능 데이터센터 수주 잔고 증가와 미국 ESS 관련 대규모 수주 실적을 근거로 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['신고가', '로봇주', '주가 상승']</t>
+          <t>['신고가', '수주잔고', 'ESS']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9300</v>
+        <v>9380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.51%</t>
+          <t>'+8.44%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>88</v>
       </c>
       <c r="F5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="H5" t="n">
         <v>5.34</v>
@@ -886,7 +886,7 @@
         <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>20294422375</v>
+        <v>20718174080</v>
       </c>
       <c r="P5" t="n">
         <v>14940</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>225250</v>
+        <v>224750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.50%</t>
+          <t>'+6.26%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G6" t="n">
-        <v>1751</v>
+        <v>1786</v>
       </c>
       <c r="H6" t="n">
         <v>46.08</v>
@@ -978,7 +978,7 @@
         <v>46.04</v>
       </c>
       <c r="O6" t="n">
-        <v>1948397905500</v>
+        <v>1993105751750</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1299000</v>
+        <v>1295000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.21%</t>
+          <t>'+5.89%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="G7" t="n">
-        <v>1662</v>
+        <v>1643</v>
       </c>
       <c r="H7" t="n">
         <v>48.77</v>
@@ -1070,7 +1070,7 @@
         <v>48.81</v>
       </c>
       <c r="O7" t="n">
-        <v>2912670189500</v>
+        <v>2967366382500</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>자사주 매입 완료 후 숨통 트임. 외인, 기관 동반 매수세 유입으로 반등 기대.</t>
+          <t>자사주 매입 종료 후 마이크론 파업 관련 속보와 함께 금융기관 매도세 관찰. 일부에서는 외인/기관 순매수를 긍정적 신호로 해석하나, 솔리다임 상장 관련 부정적 전망도 공존.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['자사주 매입', '외인 기관', '반등']</t>
+          <t>['자사주 매입', '마이크론', '솔리다임']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14690</v>
+        <v>14770</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.74%</t>
+          <t>'+4.31%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H8" t="n">
         <v>9.82</v>
@@ -1153,7 +1153,7 @@
         <v>14340</v>
       </c>
       <c r="L8" t="n">
-        <v>14780</v>
+        <v>14790</v>
       </c>
       <c r="M8" t="n">
         <v>14340</v>
@@ -1162,7 +1162,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>19681884090</v>
+        <v>20929847050</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외국인, 연기금 순매수세 확인. 목표가 5만원 제시. 대차해지 중요성 강조. 정치적 이슈 언급.</t>
+          <t>뉴스 언급에도 불구하고 주가 부진에 대한 불만 표출. 일부에서는 외인/연기금 매수를 기대하나, 전반적으로 실적 및 주가 흐름에 대한 부정적 인식이 지배적.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외인 연기금', '실적주', '목표가']</t>
+          <t>['실적주', '대차', '공매']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7470</v>
+        <v>7480</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.75%</t>
+          <t>'+2.89%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="H9" t="n">
         <v>25.45</v>
@@ -1245,7 +1245,7 @@
         <v>7360</v>
       </c>
       <c r="L9" t="n">
-        <v>7490</v>
+        <v>7520</v>
       </c>
       <c r="M9" t="n">
         <v>7250</v>
@@ -1254,7 +1254,7 @@
         <v>25.4</v>
       </c>
       <c r="O9" t="n">
-        <v>8255866350</v>
+        <v>8906366170</v>
       </c>
       <c r="P9" t="n">
         <v>17950</v>
@@ -1320,7 +1320,7 @@
         <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H10" t="n">
         <v>5.82</v>
@@ -1346,7 +1346,7 @@
         <v>5.91</v>
       </c>
       <c r="O10" t="n">
-        <v>15891727104</v>
+        <v>15939945374</v>
       </c>
       <c r="P10" t="n">
         <v>19950</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>64200</v>
+        <v>17690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.23%</t>
+          <t>'+2.14%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>388</v>
+        <v>176</v>
       </c>
       <c r="H11" t="n">
-        <v>22.23</v>
+        <v>27.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,130 +1423,130 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>62800</v>
+        <v>17320</v>
       </c>
       <c r="K11" t="n">
-        <v>63600</v>
+        <v>17480</v>
       </c>
       <c r="L11" t="n">
-        <v>64800</v>
+        <v>17820</v>
       </c>
       <c r="M11" t="n">
-        <v>62600</v>
+        <v>17170</v>
       </c>
       <c r="N11" t="n">
-        <v>22.29</v>
+        <v>27.78</v>
       </c>
       <c r="O11" t="n">
-        <v>55807417850</v>
+        <v>26650730885</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>17170</v>
       </c>
       <c r="R11" t="n">
-        <v>-40000</v>
+        <v>146000</v>
       </c>
       <c r="S11" t="n">
-        <v>-3000</v>
+        <v>24000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>야간 선물 상승에도 불구하고 국내 증시 하락세 지속. 공매도 금지 청원 등 규제 완화 요구.</t>
+          <t>정치적 비난과 함께 실적 및 조선업 섹터 전반에 대한 부정적 전망. 반도체 섹터로의 이동 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '주가 누르기', '규제 완화']</t>
+          <t>['조선업', '실적 부진', '반도체 이동']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17700</v>
+        <v>1604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.19%</t>
+          <t>'+1.97%</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="E12" t="n">
+        <v>68</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43</v>
+      </c>
+      <c r="G12" t="n">
+        <v>195</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1573</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1650</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1715</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1573</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O12" t="n">
+        <v>27428106111</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2970</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>890</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-746000</v>
+      </c>
+      <c r="S12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>78</v>
-      </c>
-      <c r="F12" t="n">
-        <v>47</v>
-      </c>
-      <c r="G12" t="n">
-        <v>172</v>
-      </c>
-      <c r="H12" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>17320</v>
-      </c>
-      <c r="K12" t="n">
-        <v>17480</v>
-      </c>
-      <c r="L12" t="n">
-        <v>17820</v>
-      </c>
-      <c r="M12" t="n">
-        <v>17170</v>
-      </c>
-      <c r="N12" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="O12" t="n">
-        <v>25710026415</v>
-      </c>
-      <c r="P12" t="n">
-        <v>35350</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>17170</v>
-      </c>
-      <c r="R12" t="n">
-        <v>146000</v>
-      </c>
-      <c r="S12" t="n">
-        <v>24000</v>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 비난과 함께 실적 및 조선업 섹터 전반에 대한 부정적 전망. 반도체 섹터로의 이동 언급.</t>
+          <t>스페이스X 수혜 기대감 속 거래량 증가. 단기 급등 가능성 있으나 윗꼬리 부담.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선업', '실적 부진', '반도체 이동']</t>
+          <t>['스페이스X', '수혜주', '거래량']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1599</v>
+        <v>64000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.65%</t>
+          <t>'+1.91%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.93</v>
+        <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>139</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G13" t="n">
-        <v>190</v>
+        <v>390</v>
       </c>
       <c r="H13" t="n">
-        <v>0.84</v>
+        <v>22.23</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,60 +1607,60 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1573</v>
+        <v>62800</v>
       </c>
       <c r="K13" t="n">
-        <v>1650</v>
+        <v>63600</v>
       </c>
       <c r="L13" t="n">
-        <v>1715</v>
+        <v>64800</v>
       </c>
       <c r="M13" t="n">
-        <v>1573</v>
+        <v>62600</v>
       </c>
       <c r="N13" t="n">
-        <v>1.77</v>
+        <v>22.29</v>
       </c>
       <c r="O13" t="n">
-        <v>27333259726</v>
+        <v>56669517250</v>
       </c>
       <c r="P13" t="n">
-        <v>2970</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>890</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>-746000</v>
+        <v>-40000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>스페이스X 수혜 기대감 속 거래량 증가. 단기 급등 가능성 있으나 윗꼬리 부담.</t>
+          <t>야간 선물 상승에도 불구하고 국내 증시 하락세 지속. 공매도 금지 청원 등 규제 완화 요구.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['스페이스X', '수혜주', '거래량']</t>
+          <t>['공매도', '주가 누르기', '규제 완화']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1671,18 +1671,18 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3100</v>
+        <v>3090</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.17%</t>
+          <t>'-4.48%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.73</v>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F14" t="n">
         <v>30</v>
@@ -1714,7 +1714,7 @@
         <v>0.73</v>
       </c>
       <c r="O14" t="n">
-        <v>9086558468</v>
+        <v>9279679737</v>
       </c>
       <c r="P14" t="n">
         <v>7050</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4287</v>
+        <v>4280</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.41%</t>
+          <t>'-7.56%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1780,7 +1780,7 @@
         <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="H15" t="n">
         <v>8.58</v>
@@ -1806,7 +1806,7 @@
         <v>8.57</v>
       </c>
       <c r="O15" t="n">
-        <v>17913706501</v>
+        <v>18214778880</v>
       </c>
       <c r="P15" t="n">
         <v>7560</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1248</v>
+        <v>1293</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-17.89%</t>
+          <t>'-14.93%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.12</v>
       </c>
       <c r="E16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H16" t="n">
         <v>0.6899999999999999</v>
@@ -1898,7 +1898,7 @@
         <v>0.57</v>
       </c>
       <c r="O16" t="n">
-        <v>17749324079</v>
+        <v>18599103977</v>
       </c>
       <c r="P16" t="n">
         <v>3980</v>
